--- a/Planning/LAUNCH/Progress_Tees_Valley_Weekly_Plan_Week08_19Oct.xlsx
+++ b/Planning/LAUNCH/Progress_Tees_Valley_Weekly_Plan_Week08_19Oct.xlsx
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Reviewed by</t>
   </si>
   <si>
-    <t xml:space="preserve">SMSC/BV this week: Black History Month culminates (half-term Fri 23 Oct) — fold the celebration into Launch's adult-ready portfolios and RE viva week.  EVIDENCE: showcase photos + EFL: cultural; complete this half-term's rows in the SMSC Evidence Tracker before break.</t>
+    <t xml:space="preserve">SMSC/BV this week: Black History Month culminates (half-term Fri 23 Oct) — fold the celebration into Launch's adult-ready portfolios and RE viva week.  EVIDENCE: showcase photos + evidence platform: cultural; complete this half-term's rows in the SMSC Evidence Tracker before break.</t>
   </si>
   <si>
     <t xml:space="preserve">Subject</t>
@@ -209,7 +209,7 @@
   </si>
   <si>
     <t xml:space="preserve">TA curates portfolios alongside pupils; teacher hosts warm, low-pressure presentations; this is a celebration of readiness, not a test.
-LOOP [Feedback Policy]: Voice = recorded micro-interview / script-flip / portfolio piece [VF] → Audience: listen fully, name one strength + one [NS] before tagging; then [R] → EVIDENCE: recording/portfolio to EFL, same day [E: PfA/careers/transition — weekly PfA minimum].</t>
+LOOP [Feedback Policy]: Voice = recorded micro-interview / script-flip / portfolio piece [VF] → Audience: listen fully, name one strength + one [NS] before tagging; then [R] → EVIDENCE: recording/portfolio to evidence platform, same day [E: PfA/careers/transition — weekly PfA minimum].</t>
   </si>
   <si>
     <t xml:space="preserve">Influence: feeds each pupil's real destination (college/barbering) → PfA plan and IEDP Outcome 5 [NS].</t>
